--- a/order_management/_Order Management - Feasibility Summary.xlsx
+++ b/order_management/_Order Management - Feasibility Summary.xlsx
@@ -821,16 +821,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>13</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>6</v>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24.6-a, 24.6-b, 24.6-c, 24.6-e, 24.6-f, 24.6-g, 24.6-h, 24.6-i, 24.6-j, 24.6-k, 24.6-l, 24.6-l2, 24.6-m, 24.6-n, 24.6-o, 24.6-p, 24.6-q</t>
+          <t>24.6-a, 24.6-b, 24.6-c, 24.6-d, 24.6-e, 24.6-f, 24.6-g, 24.6-h, 24.6-i, 24.6-j, 24.6-k, 24.6-l, 24.6-l2, 24.6-m, 24.6-n, 24.6-o, 24.6-p, 24.6-q</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Detail read model opened from the 24.1 list row id (24.1 introduces no separate route — its clickable-row requirement 24.1-c is served by the list endpoint exposing the id, so 24.1 was dropped from this endpoint's stories[]). Display of notes/invoice-note/terms (24.6-c/e/f) lives here; the WRITE for those fields is consolidated on PATCH .../notes (24.14).</t>
+          <t>Detail read model opened from the 24.1 list row id (24.1 introduces no separate route — its clickable-row requirement 24.1-c is served by the list endpoint exposing the id, so 24.1 was dropped from this endpoint's stories[]). Display of notes/payment-memo/invoice-note/terms (24.6-c/d/e/f) lives here (columns shipped by 24.14, merged to dev 2026-07-03); the WRITE for those fields is consolidated on PATCH .../notes (24.14).</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3165,130 +3165,118 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24.6-d</t>
+          <t>24.9-i</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Not Deliverable — payment-memo display/edit is not modeled on Order; feasible payment-memo writes are handled by the 24.14 notes endpoint.</t>
+          <t>Out of Scope — refund-reason QuickBooks/accounting tracking.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24.9-i</t>
+          <t>24.10-h</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Out of Scope — refund-reason QuickBooks/accounting tracking.</t>
+          <t>Blocked — no Refund model exists to record/track refund activity; no endpoint.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24.10-h</t>
+          <t>24.10-j</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Blocked — no Refund model exists to record/track refund activity; no endpoint.</t>
+          <t>Out of Scope — managing refunds individually at the plan level instead of cancelling.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>24.10-j</t>
+          <t>24.12-d</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Out of Scope — managing refunds individually at the plan level instead of cancelling.</t>
+          <t>Blocked — no Social Tables/floorplan integration for automatic booth release; no endpoint.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24.12-d</t>
+          <t>24.13-j</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Blocked — no Social Tables/floorplan integration for automatic booth release; no endpoint.</t>
+          <t>Out of Scope — operational note about creating floorplan inventory before retrying.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24.13-j</t>
+          <t>24.15-a</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Out of Scope — operational note about creating floorplan inventory before retrying.</t>
+          <t>Cron-only / Blocked — automatic upcoming-payment reminder trigger; no REST endpoint.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>24.15-a</t>
+          <t>24.15-b</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cron-only / Blocked — automatic upcoming-payment reminder trigger; no REST endpoint.</t>
+          <t>Cron-only / Blocked — automatic overdue-payment reminder trigger; no REST endpoint.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24.15-b</t>
+          <t>24.15-d</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cron-only / Blocked — automatic overdue-payment reminder trigger; no REST endpoint.</t>
+          <t>No endpoint — payment-reminder templates are provided via seed/config, not an API.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24.15-d</t>
+          <t>24.15-f</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>No endpoint — payment-reminder templates are provided via seed/config, not an API.</t>
+          <t>Cron-only / Blocked — reminder stop-on-Paid logic runs in the scheduled job, not an endpoint.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>24.15-f</t>
+          <t>24.15-h</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Cron-only / Blocked — reminder stop-on-Paid logic runs in the scheduled job, not an endpoint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>24.15-h</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>UI-only — 'no dedicated screen' statement; no endpoint.</t>
         </is>

--- a/order_management/_Order Management - Feasibility Summary.xlsx
+++ b/order_management/_Order Management - Feasibility Summary.xlsx
@@ -776,11 +776,15 @@
           <t>Quick Actions Per Order Item</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -794,19 +798,25 @@
       <c r="H6" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>11</v>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11 to build</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>2</v>
+          <t>10 to build (scope confirmed 2026-07-03; 24.5-d deferred)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1261,10 +1271,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>13</v>
@@ -1278,8 +1288,10 @@
       <c r="H17" s="8" t="n">
         <v>147</v>
       </c>
-      <c r="I17" s="9" t="n">
-        <v>140</v>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
@@ -1298,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1477,27 +1489,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/actions</t>
+          <t>/api/v1/orders/:id/agreement.pdf</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Return the permission- and status-gated set of available quick actions for an order (e.g. Booth Build only when completed/signed and the caller holds the Booth Build role).</t>
+          <t>Stream the SIGNED contract as PDF — net-new pdfmake composition over the order-snapshot context (no signed-PDF renderer existed anywhere).</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.5, 24.6</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24.5-a, 24.5-d, 24.5-l</t>
+          <t>24.5-f, 24.6-s</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Drives which quick-action buttons render; the actions themselves are the sibling POST/GET endpoints below.</t>
+          <t>Scope decision 2026-07-03: agreement downloads are the SIGNED contract (order = signed; cart = unsigned draft). 24.6-s maps onto both formats; no separate 24.6 route.</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1521,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/agreement.pdf</t>
+          <t>/api/v1/orders/:id/agreement.docx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Stream the order agreement as PDF (reuses AgreementDocumentService / buildSimplePdf), built from OrderAgreement.</t>
+          <t>Stream the SIGNED booth contract DOCX — port of exhibitor buildSignedBoothContractDocx (Order snapshot + frozen terms + filled signature block), cache-first on OrderAgreement.signed_agreement_url (shared with the exhibitor download).</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1524,12 +1536,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24.5-f, 24.6-s</t>
+          <t>24.5-e, 24.6-s</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>PDF variant of the order agreement download. 24.6-s (view/download agreement) is format-agnostic and maps onto both the .pdf and .docx routes — 24.6 introduces no separate agreement route (its invented /agreement/download was removed). Follows the existing cart agreement.pdf route convention.</t>
+          <t>Port precedent: admin ppl-order agreement-document.service. Scope decision 2026-07-03 (signed, not live-cart draft).</t>
         </is>
       </c>
     </row>
@@ -1541,44 +1553,44 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/agreement.docx</t>
+          <t>/api/v1/orders/:id/invoices/:invoiceId/invoice</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Stream the order agreement as Word/DOCX (reuses AgreementDocumentService), reflecting booth details/pricing/terms.</t>
+          <t>Generate (or return cached) the invoice PDF for an invoice belonging to the order — net-new booth/product layout over the typed line-item tree; cache-first on Invoice.invoice_pdf_url.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24.5, 24.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24.5-e, 24.6-s</t>
+          <t>24.5-g</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>DOCX variant of the same agreement generator. Two routes kept (matching the existing cart agreement.docx / agreement.pdf convention) rather than one format-query endpoint — these are distinct formats, not duplicates.</t>
+          <t>Reshaped 2026-07-03 to mirror the shipped PPL route (booth orders have one Invoice per installment).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/invoice.pdf</t>
+          <t>/api/v1/orders/:id/invite-user</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Stream the order invoice PDF from the order's written Invoice rows.</t>
+          <t>Admin adds a portal-user email ID for the order's company (invitation token + email; one email per call — port of the SBE-748 cart invite action keyed off order.company_id).</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1588,12 +1600,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24.5-g</t>
+          <t>24.5-h</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Distinct from the agreement document; sourced from Invoice rows.</t>
+          <t>Renamed from additional-users 2026-07-03 to mirror the shipped cart convention. Exhibitor-permissions clause flagged for BA removal.</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1617,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/additional-users</t>
+          <t>/api/v1/orders/:id/resend-confirmation</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Admin adds one or more portal-user email IDs for the order's company; invitation sent, per-user permissions set later by the exhibitor.</t>
+          <t>Resend booth_order_confirmation with the latest invoice PDF attached (throttled) — port of admin PPL resendOrderConfirmation.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1620,10 +1632,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24.5-h</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>24.5-i</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Distinct from POST .../send-email (24.6) which dispatches an admin-selected template; this resends the fixed confirmation.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1633,12 +1649,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/resend-confirmation</t>
+          <t>/api/v1/orders/:id/resend-portal-password</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Resend the order confirmation email (with invoice details) to the customer via mailer.sendFromTemplate.</t>
+          <t>Send the admin_resend_portal_access portal password email for the order's customer (logged) — port of admin PPL resendPortalPassword.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1648,14 +1664,10 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24.5-i</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Distinct from POST .../send-email (24.6) which dispatches an admin-selected template; this resends the fixed confirmation.</t>
-        </is>
-      </c>
+          <t>24.5-j, 24.5-m</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1665,12 +1677,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/resend-portal-password</t>
+          <t>/api/v1/orders/:id/impersonate</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Trigger a portal password-reset / temp-password email for the order's customer (logged).</t>
+          <t>Permission-based login as the order company's primary exhibitor (exhibitor JWTs, impersonated_by logged) — port of SBE-748 CartImpersonateService.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1680,10 +1692,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24.5-j, 24.5-m</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>24.5-k, 24.5-m</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Reuses the impersonate(company_id) primitive in ppl-service-provider-overview.service.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1693,44 +1709,44 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/impersonate</t>
+          <t>/api/v1/orders/:id/send-email</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Permission-gated login as the order company's primary exhibitor (mint exhibitor portal JWTs), logged via impersonated_by.</t>
+          <t>Send an order email using an admin-selected notification template (dropdown sourced from the notification-template list; dispatch via MailerService.sendFromTemplate).</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24.5-k, 24.5-m</t>
+          <t>24.6-r</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Reuses the impersonate(company_id) primitive in ppl-service-provider-overview.service.</t>
+          <t>Kept separate from resend-confirmation (24.5-i): this is template-selectable. Reuses notification-template module + background-worker MailerService.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/send-email</t>
+          <t>/api/v1/orders/:id/sales-rep</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Send an order email using an admin-selected notification template (dropdown sourced from the notification-template list; dispatch via MailerService.sendFromTemplate).</t>
+          <t>Reassign the Assigned Sales Rep / Deal Owner (permission-gated, reusing the cart assertAssignableDealOwner pattern but writing Order.sales_person_id) and trigger the HubSpot Deal Owner update.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1740,29 +1756,29 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24.6-r</t>
+          <t>24.6-t, 24.6-u, 24.6-v, 24.6-y</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Kept separate from resend-confirmation (24.5-i): this is template-selectable. Reuses notification-template module + background-worker MailerService.</t>
+          <t>Reuses cart deal-owner assignable-user logic. HubSpot Deal Owner update sub-action currently blocked.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/sales-rep</t>
+          <t>/api/v1/orders/:id/hubspot-sync</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Reassign the Assigned Sales Rep / Deal Owner (permission-gated, reusing the cart assertAssignableDealOwner pattern but writing Order.sales_person_id) and trigger the HubSpot Deal Owner update.</t>
+          <t>Manually sync the order to HubSpot (create contact/company/deal via existing client).</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1772,12 +1788,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24.6-t, 24.6-u, 24.6-v, 24.6-y</t>
+          <t>24.6-x</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Reuses cart deal-owner assignable-user logic. HubSpot Deal Owner update sub-action currently blocked.</t>
+          <t>Persisting the returned deal id needs a net-new hubspot_deal_id column on Order.</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1805,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/hubspot-sync</t>
+          <t>/api/v1/orders/:id/quickbooks-sync</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Manually sync the order to HubSpot (create contact/company/deal via existing client).</t>
+          <t>Force-sync invoices, payments, and customers for the order to QuickBooks.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1804,61 +1820,57 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24.6-x</t>
+          <t>24.6-w</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Persisting the returned deal id needs a net-new hubspot_deal_id column on Order.</t>
+          <t>BLOCKED — no QuickBooks integration exists yet.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/quickbooks-sync</t>
+          <t>/api/v1/orders/:id/payment-status</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Force-sync invoices, payments, and customers for the order to QuickBooks.</t>
+          <t>Admin manually sets a manual-method order's payment status to Paid or Unpaid; server-side validation, @Permissions check, method-eligibility gate, and an AdminAuditLog write in one transaction.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24.6-w</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED — no QuickBooks integration exists yet.</t>
-        </is>
-      </c>
+          <t>24.7-b, 24.7-c, 24.7-d</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/payment-status</t>
+          <t>/api/v1/orders/:id/payments</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Admin manually sets a manual-method order's payment status to Paid or Unpaid; server-side validation, @Permissions check, method-eligibility gate, and an AdminAuditLog write in one transaction.</t>
+          <t>The order's Payments view backing the admin Payments screen: current paid/unpaid status, payment method, amounts, and installment/transaction rows.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1868,10 +1880,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24.7-b, 24.7-c, 24.7-d</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t>24.7-a, 24.7-e</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Overlaps in data with GET .../payment-plan (24.8) but kept distinct: this backs the Payments screen (status/method focus); payment-plan backs installment management (Unallocated Balance, 60/30-day warnings).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1881,44 +1897,44 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/payments</t>
+          <t>/api/v1/orders/:id/payment-plan</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The order's Payments view backing the admin Payments screen: current paid/unpaid status, payment method, amounts, and installment/transaction rows.</t>
+          <t>The order's installments (PaymentTransaction rows) with Invoice #, date, status, amount due, order total, amount paid, plus computed Unallocated Balance and 60/30-day warnings.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24.7-a, 24.7-e</t>
+          <t>24.8-a, 24.8-h, 24.8-i</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Overlaps in data with GET .../payment-plan (24.8) but kept distinct: this backs the Payments screen (status/method focus); payment-plan backs installment management (Unallocated Balance, 60/30-day warnings).</t>
+          <t>Read side of the payment-plan management sub-resource.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/payment-plan</t>
+          <t>/api/v1/orders/:id/payment-plan/installments</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>The order's installments (PaymentTransaction rows) with Invoice #, date, status, amount due, order total, amount paid, plus computed Unallocated Balance and 60/30-day warnings.</t>
+          <t>Manually add a new installment (incl. non-card types once schema relaxed); validates Unallocated Balance remains, runs the 60/30-day rule (warn/bypass for authorized users), enforces totals server-side.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1928,29 +1944,25 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24.8-a, 24.8-h, 24.8-i</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Read side of the payment-plan management sub-resource.</t>
-        </is>
-      </c>
+          <t>24.8-f, 24.8-i, 24.8-j, 24.8-k, 24.8-m</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/payment-plan/installments</t>
+          <t>/api/v1/orders/:id/payment-plan/installments/:installmentId</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Manually add a new installment (incl. non-card types once schema relaxed); validates Unallocated Balance remains, runs the 60/30-day rule (warn/bypass for authorized users), enforces totals server-side.</t>
+          <t>Edit a future installment's date, or mark it Paid/Unpaid/Refund; enforces post-payment lock (Refund-only after paid), date rules with warning-bypass, milestone-status/QuickBooks action, and backend total enforcement.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1960,15 +1972,19 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24.8-f, 24.8-i, 24.8-j, 24.8-k, 24.8-m</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>24.8-b, 24.8-c, 24.8-d, 24.8-g, 24.8-j, 24.8-k, 24.8-l, 24.8-m</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The mark-as-Paid capability here is what the 24.15 payment-reminder cron's stop-condition depends on.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1978,7 +1994,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Edit a future installment's date, or mark it Paid/Unpaid/Refund; enforces post-payment lock (Refund-only after paid), date rules with warning-bypass, milestone-status/QuickBooks action, and backend total enforcement.</t>
+          <t>Delete an unpaid installment and return its amount to the Unallocated Balance; blocked when the installment is already paid.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1988,39 +2004,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24.8-b, 24.8-c, 24.8-d, 24.8-g, 24.8-j, 24.8-k, 24.8-l, 24.8-m</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The mark-as-Paid capability here is what the 24.15 payment-reminder cron's stop-condition depends on.</t>
-        </is>
-      </c>
+          <t>24.8-e, 24.8-g, 24.8-h</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/payment-plan/installments/:installmentId</t>
+          <t>/api/v1/orders/:id/refund-options</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Delete an unpaid installment and return its amount to the Unallocated Balance; blocked when the installment is already paid.</t>
+          <t>Return available refund methods (always Manual; Stripe only when the order/installment has a stripe_charge_id) and the refundable cap (paid_amount minus prior refunds).</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24.8-e, 24.8-g, 24.8-h</t>
+          <t>24.9-d, 24.9-f</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -2028,30 +2040,34 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/refund-options</t>
+          <t>/api/v1/orders/:id/refunds</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Return available refund methods (always Manual; Stripe only when the order/installment has a stripe_charge_id) and the refundable cap (paid_amount minus prior refunds).</t>
+          <t>Issue a Manual or Stripe refund for the order's payment plan: validate cap + mandatory reason, persist a net-new Refund record, set payment-plan status to Refunded (manual, or on Stripe success) or Refund Failed (Stripe failure); optionally email a refund notice.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.9, 24.6, 24.11</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24.9-d, 24.9-f</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+          <t>24.9-a, 24.9-b, 24.9-c, 24.9-d, 24.9-e, 24.9-g, 24.9-h, 24.6-z, 24.11-a, 24.11-b, 24.11-c, 24.11-d, 24.11-e</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ONE canonical refund endpoint owned by 24.9. Consolidates 24.6-z's refund half (its bundled refund+void entry was split — void is a separate endpoint) and 24.11's refund-email notice. Accepts send_notification (default true) which emails the exhibitor via MailerService.sendFromTemplate (24.11). Calls external-api-service POST /v1/refunds for the Stripe leg. Neither 24.6 nor 24.11 introduces a separate refund route.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2061,27 +2077,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/refunds</t>
+          <t>/api/v1/orders/:id/void</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Issue a Manual or Stripe refund for the order's payment plan: validate cap + mandatory reason, persist a net-new Refund record, set payment-plan status to Refunded (manual, or on Stripe success) or Refund Failed (Stripe failure); optionally email a refund notice.</t>
+          <t>Initiate a void on the order's payment.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24.9, 24.6, 24.11</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24.9-a, 24.9-b, 24.9-c, 24.9-d, 24.9-e, 24.9-g, 24.9-h, 24.6-z, 24.11-a, 24.11-b, 24.11-c, 24.11-d, 24.11-e</t>
+          <t>24.6-z</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ONE canonical refund endpoint owned by 24.9. Consolidates 24.6-z's refund half (its bundled refund+void entry was split — void is a separate endpoint) and 24.11's refund-email notice. Accepts send_notification (default true) which emails the exhibitor via MailerService.sendFromTemplate (24.11). Calls external-api-service POST /v1/refunds for the Stripe leg. Neither 24.6 nor 24.11 introduces a separate refund route.</t>
+          <t>Void half of 24.6-z, split from refund. BLOCKED — no Stripe void execution path or Refund model exists yet.</t>
         </is>
       </c>
     </row>
@@ -2093,27 +2109,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/void</t>
+          <t>/api/v1/orders/:id/cancel</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Initiate a void on the order's payment.</t>
+          <t>Cancel an entire order: validate &amp; cap refund against Order.paid_amount, set Order.status=canceled, flip unpaid/pending/scheduled PaymentTransactions to canceled, release all committed InventoryReservation rows (booths + other products) in one transaction, initiate the Stripe refund via stripe_charge_id, return a manual-floorplan-release reminder when booth lines were present, optionally email a cancellation notice, and write an AdminAuditLog (entity_type=order).</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.10, 24.11, 24.12</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24.6-z</t>
+          <t>24.10-a, 24.10-b, 24.10-c, 24.10-d, 24.10-e, 24.10-f, 24.10-g, 24.10-i, 24.11-a, 24.11-b, 24.11-c, 24.11-d, 24.11-e, 24.12-a, 24.12-b, 24.12-c, 24.12-e, 24.12-f</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Void half of 24.6-z, split from refund. BLOCKED — no Stripe void execution path or Refund model exists yet.</t>
+          <t>ONE cancel endpoint owned by 24.10, merging the three sibling stories that each proposed POST .../cancel: 24.10 (refund cap + status flip + Stripe refund + audit log), 24.11 (send_notification, default true, cancellation email), and 24.12 (release InventoryReservation rows + manual floorplan-release reminder flag). 24.11 and 24.12 introduce no separate route. All server-side enforced; explicit confirmation captured client-side.</t>
         </is>
       </c>
     </row>
@@ -2125,27 +2141,27 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/cancel</t>
+          <t>/api/v1/orders/:id/move-show/validate</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Cancel an entire order: validate &amp; cap refund against Order.paid_amount, set Order.status=canceled, flip unpaid/pending/scheduled PaymentTransactions to canceled, release all committed InventoryReservation rows (booths + other products) in one transaction, initiate the Stripe refund via stripe_charge_id, return a manual-floorplan-release reminder when booth lines were present, optionally email a cancellation notice, and write an AdminAuditLog (entity_type=order).</t>
+          <t>Pre-validate moving an order to a chosen destination show: confirm equivalent booth(s) + included products exist with sufficient inventory; return the unavailability reason without mutating anything.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24.10, 24.11, 24.12</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24.10-a, 24.10-b, 24.10-c, 24.10-d, 24.10-e, 24.10-f, 24.10-g, 24.10-i, 24.11-a, 24.11-b, 24.11-c, 24.11-d, 24.11-e, 24.12-a, 24.12-b, 24.12-c, 24.12-e, 24.12-f</t>
+          <t>24.13-e, 24.13-f, 24.13-g</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>ONE cancel endpoint owned by 24.10, merging the three sibling stories that each proposed POST .../cancel: 24.10 (refund cap + status flip + Stripe refund + audit log), 24.11 (send_notification, default true, cancellation email), and 24.12 (release InventoryReservation rows + manual floorplan-release reminder flag). 24.11 and 24.12 introduce no separate route. All server-side enforced; explicit confirmation captured client-side.</t>
+          <t>Dry-run companion to the move-show execute endpoint — a distinct validate-only operation, not a duplicate of move-show.</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2173,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/move-show/validate</t>
+          <t>/api/v1/orders/:id/move-show</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Pre-validate moving an order to a chosen destination show: confirm equivalent booth(s) + included products exist with sufficient inventory; return the unavailability reason without mutating anything.</t>
+          <t>Execute a direct transfer in one $transaction: re-map every order line to the destination show's ShowProduct (same product_id), release source-show committed reservations (status-&gt;released by order_id), re-commit destination reservations under a FOR UPDATE lock; reject in-move edits; fail with a clear message if inventory is unavailable.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2172,47 +2188,47 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24.13-e, 24.13-f, 24.13-g</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run companion to the move-show execute endpoint — a distinct validate-only operation, not a duplicate of move-show.</t>
-        </is>
-      </c>
+          <t>24.13-a, 24.13-b, 24.13-c, 24.13-d, 24.13-g, 24.13-h, 24.13-i</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/move-show</t>
+          <t>/api/v1/orders/:id/notes</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Execute a direct transfer in one $transaction: re-map every order line to the destination show's ShowProduct (same product_id), release source-show committed reservations (status-&gt;released by order_id), re-commit destination reservations under a FOR UPDATE lock; reject in-move edits; fail with a clear message if inventory is unavailable.</t>
+          <t>Return the order's internal notes, payment memo, invoice/PO note, and additional terms for the admin Order Details -&gt; Notes tab.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24.13-a, 24.13-b, 24.13-c, 24.13-d, 24.13-g, 24.13-h, 24.13-i</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+          <t>24.14-a, 24.14-b, 24.14-c, 24.14-d, 24.14-f</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Dedicated notes sub-resource (read).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2222,86 +2238,86 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Return the order's internal notes, payment memo, invoice/PO note, and additional terms for the admin Order Details -&gt; Notes tab.</t>
+          <t>Add/edit internal notes, payment memo, invoice/PO note, and additional terms in one Prisma transaction, recording an AdminAuditLog (entity_type=order) per change. Behind JWT + roles + @Permissions.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.14, 24.6</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24.14-a, 24.14-b, 24.14-c, 24.14-d, 24.14-f</t>
+          <t>24.14-a, 24.14-b, 24.14-c, 24.14-d, 24.14-e, 24.14-g, 24.6-c, 24.6-e, 24.6-f</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Dedicated notes sub-resource (read).</t>
+          <t>Canonical write path for notes/additional-terms; absorbs the notes-editing concern that 24.6's PATCH /api/v1/orders/:id originally referenced (24.6-c/e/f), so those fields have a single mutation route. 24.6 introduces no separate notes-write route.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/orders/:id/notes</t>
+          <t>/api/v1/logs/admin-audit?entity_type=order&amp;entity_id=:id</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Add/edit internal notes, payment memo, invoice/PO note, and additional terms in one Prisma transaction, recording an AdminAuditLog (entity_type=order) per change. Behind JWT + roles + @Permissions.</t>
+          <t>List the permanent, non-editable audit-trail entries for an order's note changes.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24.14, 24.6</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24.14-a, 24.14-b, 24.14-c, 24.14-d, 24.14-e, 24.14-g, 24.6-c, 24.6-e, 24.6-f</t>
+          <t>24.14-e</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Canonical write path for notes/additional-terms; absorbs the notes-editing concern that 24.6's PATCH /api/v1/orders/:id originally referenced (24.6-c/e/f), so those fields have a single mutation route. 24.6 introduces no separate notes-write route.</t>
+          <t>ALREADY BUILT — the existing admin-audit-log.controller GET / route already exposes entity_type (AdminAuditEntityType includes 'order') and entity_id filters; no new endpoint required. A dedicated alias /api/v1/orders/:id/notes/audit-trail is optional sugar.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/logs/admin-audit?entity_type=order&amp;entity_id=:id</t>
+          <t>background-worker-service: /manual-trigger/payment-reminders/run</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>List the permanent, non-editable audit-trail entries for an order's note changes.</t>
+          <t>Dev-only manual trigger to invoke the payment-reminder cron on demand (reuses task.run() so the cron re-entrancy guard applies).</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24.14-e</t>
+          <t>24.15-c, 24.15-e, 24.15-g</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>ALREADY BUILT — the existing admin-audit-log.controller GET / route already exposes entity_type (AdminAuditEntityType includes 'order') and entity_id filters; no new endpoint required. A dedicated alias /api/v1/orders/:id/notes/audit-trail is optional sugar.</t>
+          <t>Lives in background-worker-service, mirroring the existing @Controller('manual-trigger') + @Post('lead-distribution/run') / @Post('low-balance/run') convention. The reminder itself runs on a registered cron; no customer- or admin-facing REST/UI endpoint (story has no screen). Depends on the admin mark-as-Paid capability (PATCH .../installments/:installmentId, 24.8).</t>
         </is>
       </c>
     </row>
@@ -2313,57 +2329,25 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>background-worker-service: /manual-trigger/payment-reminders/run</t>
+          <t>external-api-service: /v1/refunds (internal)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dev-only manual trigger to invoke the payment-reminder cron on demand (reuses task.run() so the cron re-entrancy guard applies).</t>
+          <t>stripe.refunds.create wrapper against the order's stripe_charge_id, returning the Stripe refund result/status so the admin refund service can set Refunded / Refund Failed.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>24.15-c, 24.15-e, 24.15-g</t>
+          <t>24.9-b, 24.9-g</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Lives in background-worker-service, mirroring the existing @Controller('manual-trigger') + @Post('lead-distribution/run') / @Post('low-balance/run') convention. The reminder itself runs on a registered cron; no customer- or admin-facing REST/UI endpoint (story has no screen). Depends on the admin mark-as-Paid capability (PATCH .../installments/:installmentId, 24.8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>external-api-service: /v1/refunds (internal)</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>stripe.refunds.create wrapper against the order's stripe_charge_id, returning the Stripe refund result/status so the admin refund service can set Refunded / Refund Failed.</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>24.9-b, 24.9-g</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Lives in external-api-service (matches its Stripe controller convention, e.g. @Controller('v1/payment-intents')); called internally by the admin POST /api/v1/orders/:id/refunds service. Not a public/admin route.</t>
         </is>
@@ -3095,7 +3079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3282,6 +3266,30 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>24.5-a</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>No dedicated endpoint by decision (2026-07-03) — the Quick Actions menu is front-end; the backend is the union of the per-action routes, each @Permissions-gated (no /actions availability endpoint).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>24.5-d</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deferred (2026-07-03) — Booth Build quick action moves to its own future-sprint story (mirrors SBE-748); the confirmed/signed mapping question travels with it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
